--- a/06_Debt_Finance/instances/public_microsoft_2024.xlsx
+++ b/06_Debt_Finance/instances/public_microsoft_2024.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,154 +25,45 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision &amp; Checks" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="FS_DOMAIN" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$5</definedName>
-    <definedName name="FS_MATURITY" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$6</definedName>
-    <definedName name="FS_MODEL_ID" hidden="0" function="0" vbProcedure="0">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
+    <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
+    <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.0%;\(0.0%\);\-"/>
-    <numFmt numFmtId="169" formatCode="0.00%;[RED]\(0.00%\);\-"/>
-    <numFmt numFmtId="170" formatCode="0&quot; bps&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
-    <numFmt numFmtId="172" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
+    <numFmt numFmtId="166" formatCode="0.0x;[Red](0.0x);-"/>
+    <numFmt numFmtId="167" formatCode="0.00%;[Red](0.00%);-"/>
+    <numFmt numFmtId="168" formatCode="0 &quot;bps&quot;"/>
+    <numFmt numFmtId="169" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.0x"/>
+    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
@@ -180,8 +71,64 @@
       <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00111827"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -190,32 +137,34 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF17365D"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF17365D"/>
-        <bgColor rgb="FF333333"/>
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="0017365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -233,477 +182,241 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFB7B7B7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="55">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="169" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="3" fillId="8" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFD9EAF7"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFB7B7B7"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF17365D"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -711,294 +424,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="36" customWidth="1" style="47" min="2" max="2"/>
-    <col width="46" customWidth="1" style="47" min="3" max="3"/>
-    <col width="12" customWidth="1" style="47" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[ISSUER] — Debt Finance &amp; Refinancing</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="50" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Issuer:</t>
         </is>
       </c>
-      <c r="C4" s="51" t="inlineStr">
-        <is>
-          <t>[Name]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="50" t="inlineStr">
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation (NASDAQ: MSFT), CIK 0000789019</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Transaction:</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
-        <is>
-          <t>Refinancing / acquisition / general corporate</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="50" t="inlineStr">
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>FY2024 debt, liquidity, and refinancing profile -- general corporate, no transaction pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C6" s="52" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
         <is>
           <t>2024-06-30</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="50" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Next maturity / launch:</t>
         </is>
       </c>
-      <c r="C7" s="51" t="inlineStr">
-        <is>
-          <t>[date]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
+        <is>
+          <t>FY2025 (within twelve months of 2024-06-30): 8,942 $mm of tagged near-term maturities (LongTermDebtCurrent 2,249 + commercial paper 6,693)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Refresh cadence:</t>
         </is>
       </c>
-      <c r="C8" s="51" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="50" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
+        <is>
+          <t>Annual, on Microsoft's Form 10-K (fiscal year ends 30 June)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="52" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="50" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$ in millions</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="53" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="54" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="55" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="50" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="55" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="56" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="55" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="50" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="55" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -1010,133 +833,131 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="32" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="4"/>
-    <col width="22" customWidth="1" style="47" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Covenant &amp; Rating Screens</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Headroom / status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Gross leverage</t>
         </is>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="21">
         <f>'Capital Structure'!C13</f>
         <v/>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="21">
         <f>Assumptions!E18</f>
         <v/>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="21">
         <f>D5-C5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="21">
         <f>'Capital Structure'!C15</f>
         <v/>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="21">
         <f>Assumptions!E19</f>
         <v/>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="21">
         <f>C6-D6</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Near-term maturities / debt</t>
         </is>
       </c>
-      <c r="C7" s="70">
+      <c r="C7" s="16">
         <f>IFERROR(SUM('Maturity Ladder'!C10:E10)/'Capital Structure'!C10,0)</f>
         <v/>
       </c>
-      <c r="D7" s="70" t="n">
+      <c r="D7" s="16" t="n">
         <v>0.35</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="16">
         <f>D7-C7</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Refinancing status</t>
         </is>
       </c>
-      <c r="C8" s="47">
+      <c r="C8">
         <f>Refinancing!G8</f>
         <v/>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E8" s="47">
+      <c r="E8">
         <f>IF(C8=D8,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -1146,200 +967,199 @@
     <mergeCell ref="B2:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="E8">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>E8="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>E8="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>E8="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>E8="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="32" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="4"/>
-    <col width="42" customWidth="1" style="47" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Claim Recovery Waterfall</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Stressed EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="15">
         <f>Assumptions!C5</f>
         <v/>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="15">
         <f>Assumptions!D5</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Recovery multiple</t>
         </is>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="21">
         <f>Assumptions!C20</f>
         <v/>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="21">
         <f>Assumptions!D20</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="15">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="15">
         <f>D5*D6</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>EV haircut</t>
         </is>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="15">
         <f>C7*Assumptions!C21</f>
         <v/>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="15">
         <f>D7*Assumptions!D21</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="47" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Distributable value</t>
         </is>
       </c>
-      <c r="C9" s="69">
+      <c r="C9" s="15">
         <f>C7-C8</f>
         <v/>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="15">
         <f>D7-D8</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="47" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="C10" s="69">
+      <c r="C10" s="15">
         <f>'Capital Structure'!C10</f>
         <v/>
       </c>
-      <c r="D10" s="69">
+      <c r="D10" s="15">
         <f>'Capital Structure'!C10</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="47" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Recovery value</t>
         </is>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="15">
         <f>MIN(C9,C10)</f>
         <v/>
       </c>
-      <c r="D11" s="69">
+      <c r="D11" s="15">
         <f>MIN(D9,D10)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="47" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Recovery rate</t>
         </is>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="16">
         <f>IFERROR(C11/C10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="16">
         <f>IFERROR(D11/D10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="47" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>LGD</t>
         </is>
       </c>
-      <c r="C13" s="70">
+      <c r="C13" s="16">
         <f>1-C12</f>
         <v/>
       </c>
-      <c r="D13" s="70">
+      <c r="D13" s="16">
         <f>1-D12</f>
         <v/>
       </c>
@@ -1348,97 +1168,106 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="42" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Sources equal uses</t>
         </is>
       </c>
-      <c r="C5" s="47">
+      <c r="C5">
         <f>IF(Refinancing!G8="PASS","PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Debt nonnegative</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6">
         <f>IF('Capital Structure'!C10&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Maturities reconcile</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7">
         <f>IF(ABS(SUM('Maturity Ladder'!C10:H10)-'Capital Structure'!C10)&lt;0.01,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Recovery bounded</t>
         </is>
       </c>
-      <c r="C8" s="47">
+      <c r="C8">
         <f>IF(AND(MIN(Recovery!C12:D12)&gt;=0,MAX(Recovery!C12:D12)&lt;=1),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="47" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Refinancing funded without equity plug</t>
+        </is>
+      </c>
+      <c r="C9">
+        <f>IF(Refinancing!E7&lt;=0.01,"PASS","BREACH")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C9" s="47">
-        <f>IF(COUNTIF(C5:C8,"FAIL")+COUNTIF(C5:C8,"REVIEW")=0,"PASS","REVIEW")</f>
+      <c r="C10">
+        <f>IF(COUNTIF(C5:C9,"FAIL")+COUNTIF(C5:C9,"BREACH")&gt;0,"FAIL",IF(COUNTIF(C5:C9,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
     </row>
@@ -1446,200 +1275,242 @@
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:C9">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+  <conditionalFormatting sqref="C5:C10">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:E12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="34" customWidth="1" style="47" min="2" max="2"/>
-    <col width="58" customWidth="1" style="47" min="3" max="3"/>
-    <col width="16" customWidth="1" style="47" min="4" max="4"/>
-    <col width="48" customWidth="1" style="47" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="81" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Debt instruments</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t>Credit agreements, indentures, or filings</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E5" s="81" t="inlineStr">
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>Balance, rate, maturity, collateral and covenants</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="81" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Market pricing</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Treasury / swap curve and comparable new issues</t>
         </is>
       </c>
-      <c r="D6" s="81" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E6" s="81" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Freeze base-rate and spread assumptions</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="81" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Financial statements</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Audited statements or filing</t>
         </is>
       </c>
-      <c r="D7" s="81" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>[period]</t>
         </is>
       </c>
-      <c r="E7" s="81" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>EBITDA, cash and debt reconciliation</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="81" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Recovery methodology</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Documented enterprise-value and priority assumptions</t>
         </is>
       </c>
-      <c r="D8" s="81" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E8" s="81" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>Claim-level recovery bridge</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="82" t="inlineStr">
+      <c r="B9" s="51" t="inlineStr">
         <is>
           <t>Microsoft 2024 Form 10-K</t>
         </is>
       </c>
-      <c r="C9" s="82" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/789019/000095017024087843/msft-20240630.htm</t>
         </is>
       </c>
-      <c r="D9" s="82" t="inlineStr">
+      <c r="D9" s="51" t="inlineStr">
         <is>
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="E9" s="82" t="inlineStr">
-        <is>
-          <t>U.S. SEC / Microsoft; frozen curated observation as of case date</t>
+      <c r="E9" s="51" t="inlineStr">
+        <is>
+          <t>Cash-flow and liquidity disclosures frozen in the case snapshot: debt issued, debt repaid, ending debt, cash and short-term investments, operating cash flow, capex.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="51" t="inlineStr">
+        <is>
+          <t>Microsoft FY2024 XBRL company facts (CIK 0000789019)</t>
+        </is>
+      </c>
+      <c r="C10" s="51" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0000789019.json</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="E10" s="51" t="inlineStr">
+        <is>
+          <t>SEC XBRL company facts for CIK 0000789019, recorded at tools/data_fabric/out/MSFT_facts_annual_series.json. Supplies the debt balances, current/non-current split, commercial paper, cash, operating income, and interest expense for FY2024, FY2023, FY2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>Frozen source snapshot</t>
         </is>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>repo://06_Debt_Finance/sources/snapshots/debt-public-microsoft-2024.json</t>
         </is>
       </c>
-      <c r="D10" s="82" t="inlineStr">
+      <c r="D11" s="51" t="inlineStr">
         <is>
           <t>2024-06-30</t>
         </is>
       </c>
-      <c r="E10" s="82" t="inlineStr">
+      <c r="E11" s="51" t="inlineStr">
         <is>
           <t>Immutable curated observation package with SHA-256 digest</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="51" t="inlineStr">
+        <is>
+          <t>Case driver (no tagged disclosure exists)</t>
+        </is>
+      </c>
+      <c r="C12" s="51" t="inlineStr">
+        <is>
+          <t>repo://06_Debt_Finance/sources/snapshots/debt-public-microsoft-2024.json</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="E12" s="51" t="inlineStr">
+        <is>
+          <t>Floating base rate. Not company data; it would come from a rates source (FRED), which is not reachable in this environment. It feeds only the term-loan line, which is zero for Microsoft, so it is inert here.</t>
         </is>
       </c>
     </row>
@@ -1647,1709 +1518,1703 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="14" customWidth="1" style="47" min="2" max="2"/>
-    <col width="22" customWidth="1" style="47" min="3" max="3"/>
-    <col width="28" customWidth="1" style="47" min="4" max="4"/>
-    <col width="38" customWidth="1" style="47" min="5" max="5"/>
-    <col width="34" customWidth="1" style="47" min="6" max="6"/>
-    <col width="18" customWidth="1" style="47" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C5" s="83" t="inlineStr">
-        <is>
-          <t>External historical evidence materialization</t>
-        </is>
-      </c>
-      <c r="D5" s="83" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Depth pass: full input accounting against recorded XBRL facts</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>repo://06_Debt_Finance/sources/snapshots/debt-public-microsoft-2024.json</t>
         </is>
       </c>
-      <c r="E5" s="83" t="inlineStr">
-        <is>
-          <t>Generated public case debt-public-microsoft-2024 from canonical release template</t>
-        </is>
-      </c>
-      <c r="F5" s="83" t="inlineStr">
-        <is>
-          <t>External historical case; human stakeholder approval remains pending</t>
-        </is>
-      </c>
-      <c r="G5" s="83" t="inlineStr">
-        <is>
-          <t>On source revision, builder change, monitoring breach, or annual review</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="83" t="n"/>
-      <c r="C6" s="83" t="n"/>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="83" t="n"/>
-      <c r="F6" s="83" t="n"/>
-      <c r="G6" s="83" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="83" t="n"/>
-      <c r="C7" s="83" t="n"/>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n"/>
-      <c r="F7" s="83" t="n"/>
-      <c r="G7" s="83" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="83" t="n"/>
-      <c r="C8" s="83" t="n"/>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="83" t="n"/>
-      <c r="F8" s="83" t="n"/>
-      <c r="G8" s="83" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="83" t="n"/>
-      <c r="C9" s="83" t="n"/>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n"/>
-      <c r="F9" s="83" t="n"/>
-      <c r="G9" s="83" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="83" t="n"/>
-      <c r="C10" s="83" t="n"/>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="83" t="n"/>
-      <c r="F10" s="83" t="n"/>
-      <c r="G10" s="83" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="83" t="n"/>
-      <c r="C11" s="83" t="n"/>
-      <c r="D11" s="83" t="n"/>
-      <c r="E11" s="83" t="n"/>
-      <c r="F11" s="83" t="n"/>
-      <c r="G11" s="83" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="83" t="n"/>
-      <c r="C12" s="83" t="n"/>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n"/>
-      <c r="F12" s="83" t="n"/>
-      <c r="G12" s="83" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="83" t="n"/>
-      <c r="C13" s="83" t="n"/>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n"/>
-      <c r="F13" s="83" t="n"/>
-      <c r="G13" s="83" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="83" t="n"/>
-      <c r="C14" s="83" t="n"/>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="83" t="n"/>
-      <c r="F14" s="83" t="n"/>
-      <c r="G14" s="83" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="83" t="n"/>
-      <c r="C15" s="83" t="n"/>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n"/>
-      <c r="F15" s="83" t="n"/>
-      <c r="G15" s="83" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="83" t="n"/>
-      <c r="C16" s="83" t="n"/>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="83" t="n"/>
-      <c r="F16" s="83" t="n"/>
-      <c r="G16" s="83" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="83" t="n"/>
-      <c r="C17" s="83" t="n"/>
-      <c r="D17" s="83" t="n"/>
-      <c r="E17" s="83" t="n"/>
-      <c r="F17" s="83" t="n"/>
-      <c r="G17" s="83" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="B18" s="83" t="n"/>
-      <c r="C18" s="83" t="n"/>
-      <c r="D18" s="83" t="n"/>
-      <c r="E18" s="83" t="n"/>
-      <c r="F18" s="83" t="n"/>
-      <c r="G18" s="83" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="48">
-      <c r="B19" s="83" t="n"/>
-      <c r="C19" s="83" t="n"/>
-      <c r="D19" s="83" t="n"/>
-      <c r="E19" s="83" t="n"/>
-      <c r="F19" s="83" t="n"/>
-      <c r="G19" s="83" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="B20" s="83" t="n"/>
-      <c r="C20" s="83" t="n"/>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="83" t="n"/>
-      <c r="F20" s="83" t="n"/>
-      <c r="G20" s="83" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="B21" s="83" t="n"/>
-      <c r="C21" s="83" t="n"/>
-      <c r="D21" s="83" t="n"/>
-      <c r="E21" s="83" t="n"/>
-      <c r="F21" s="83" t="n"/>
-      <c r="G21" s="83" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="48">
-      <c r="B22" s="83" t="n"/>
-      <c r="C22" s="83" t="n"/>
-      <c r="D22" s="83" t="n"/>
-      <c r="E22" s="83" t="n"/>
-      <c r="F22" s="83" t="n"/>
-      <c r="G22" s="83" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="48">
-      <c r="B23" s="83" t="n"/>
-      <c r="C23" s="83" t="n"/>
-      <c r="D23" s="83" t="n"/>
-      <c r="E23" s="83" t="n"/>
-      <c r="F23" s="83" t="n"/>
-      <c r="G23" s="83" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="48">
-      <c r="B24" s="83" t="n"/>
-      <c r="C24" s="83" t="n"/>
-      <c r="D24" s="83" t="n"/>
-      <c r="E24" s="83" t="n"/>
-      <c r="F24" s="83" t="n"/>
-      <c r="G24" s="83" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="48">
-      <c r="B25" s="83" t="n"/>
-      <c r="C25" s="83" t="n"/>
-      <c r="D25" s="83" t="n"/>
-      <c r="E25" s="83" t="n"/>
-      <c r="F25" s="83" t="n"/>
-      <c r="G25" s="83" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="48">
-      <c r="B26" s="83" t="n"/>
-      <c r="C26" s="83" t="n"/>
-      <c r="D26" s="83" t="n"/>
-      <c r="E26" s="83" t="n"/>
-      <c r="F26" s="83" t="n"/>
-      <c r="G26" s="83" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="48">
-      <c r="B27" s="83" t="n"/>
-      <c r="C27" s="83" t="n"/>
-      <c r="D27" s="83" t="n"/>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
-      <c r="G27" s="83" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="48">
-      <c r="B28" s="83" t="n"/>
-      <c r="C28" s="83" t="n"/>
-      <c r="D28" s="83" t="n"/>
-      <c r="E28" s="83" t="n"/>
-      <c r="F28" s="83" t="n"/>
-      <c r="G28" s="83" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="48">
-      <c r="B29" s="83" t="n"/>
-      <c r="C29" s="83" t="n"/>
-      <c r="D29" s="83" t="n"/>
-      <c r="E29" s="83" t="n"/>
-      <c r="F29" s="83" t="n"/>
-      <c r="G29" s="83" t="n"/>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Rebuilt the case from Microsoft's recorded SEC XBRL facts. It previously carried four sourced cells out of 102 candidates (4.9%) with every other input left at a generic leveraged-mid-cap template default -- a $300mm term loan Microsoft does not have, a 5.5x leverage covenant it is not subject to, a 5.5% coupon. Capital structure now ties exactly to disclosed total debt, cash interest and weighted cost are solved to disclosed interest expense, and every remaining cell is a declared driver with a stated reason.</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>External historical case; human stakeholder approval remains pending. EBITDA is proxied by EBIT because Microsoft tags no D&amp;A concept; the bias is conservative (understates coverage, overstates leverage).</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>On Microsoft's next Form 10-K, builder change, or annual review</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="25" t="n"/>
+      <c r="F6" s="25" t="n"/>
+      <c r="G6" s="25" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
+      <c r="E7" s="25" t="n"/>
+      <c r="F7" s="25" t="n"/>
+      <c r="G7" s="25" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="25" t="n"/>
+      <c r="F8" s="25" t="n"/>
+      <c r="G8" s="25" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="25" t="n"/>
+      <c r="C9" s="25" t="n"/>
+      <c r="D9" s="25" t="n"/>
+      <c r="E9" s="25" t="n"/>
+      <c r="F9" s="25" t="n"/>
+      <c r="G9" s="25" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+      <c r="G10" s="25" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="25" t="n"/>
+      <c r="C11" s="25" t="n"/>
+      <c r="D11" s="25" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
+      <c r="G11" s="25" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
+      <c r="G12" s="25" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="25" t="n"/>
+      <c r="F14" s="25" t="n"/>
+      <c r="G14" s="25" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+      <c r="G16" s="25" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+      <c r="E17" s="25" t="n"/>
+      <c r="F17" s="25" t="n"/>
+      <c r="G17" s="25" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="25" t="n"/>
+      <c r="F18" s="25" t="n"/>
+      <c r="G18" s="25" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="25" t="n"/>
+      <c r="F20" s="25" t="n"/>
+      <c r="G20" s="25" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
+      <c r="F21" s="25" t="n"/>
+      <c r="G21" s="25" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+      <c r="G22" s="25" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+      <c r="E23" s="25" t="n"/>
+      <c r="F23" s="25" t="n"/>
+      <c r="G23" s="25" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="25" t="n"/>
+      <c r="F24" s="25" t="n"/>
+      <c r="G24" s="25" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+      <c r="G25" s="25" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+      <c r="G26" s="25" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="25" t="n"/>
+      <c r="G27" s="25" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n"/>
+      <c r="D29" s="25" t="n"/>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+      <c r="G29" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="42" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="4"/>
-    <col width="46" customWidth="1" style="47" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="48">
-      <c r="B2" s="84" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Debt Rollforward, Maturity Wall, Weighted Cost, and Coverage</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="85" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="85" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="85" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Adversarial</t>
         </is>
       </c>
-      <c r="E4" s="85" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Units / control</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Opening debt</t>
         </is>
       </c>
-      <c r="C5" s="86" t="n">
+      <c r="C5" s="52" t="n">
         <v>71802</v>
       </c>
-      <c r="D5" s="87" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+      <c r="D5" s="52" t="n">
+        <v>71802</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Issuance</t>
         </is>
       </c>
-      <c r="C6" s="86" t="n">
+      <c r="C6" s="52" t="n">
         <v>24395</v>
       </c>
-      <c r="D6" s="87" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+      <c r="D6" s="52" t="n">
+        <v>24395</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Repayments</t>
         </is>
       </c>
-      <c r="C7" s="86" t="n">
+      <c r="C7" s="52" t="n">
         <v>29070</v>
       </c>
-      <c r="D7" s="87" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+      <c r="D7" s="52" t="n">
+        <v>29070</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Year 1 maturity</t>
         </is>
       </c>
-      <c r="C8" s="87" t="n">
-        <v>50</v>
-      </c>
-      <c r="D8" s="87" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="47" t="inlineStr">
+      <c r="C8" s="52" t="n">
+        <v>8942</v>
+      </c>
+      <c r="D8" s="52" t="n">
+        <v>8942</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Year 2 maturity</t>
         </is>
       </c>
-      <c r="C9" s="87" t="n">
-        <v>75</v>
-      </c>
-      <c r="D9" s="87" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="47" t="inlineStr">
+      <c r="C9" s="52" t="n">
+        <v>12800.7</v>
+      </c>
+      <c r="D9" s="52" t="n">
+        <v>12800.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Year 3 maturity</t>
         </is>
       </c>
-      <c r="C10" s="87" t="n">
-        <v>100</v>
-      </c>
-      <c r="D10" s="87" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="47" t="inlineStr">
+      <c r="C10" s="52" t="n">
+        <v>13964.4</v>
+      </c>
+      <c r="D10" s="52" t="n">
+        <v>13964.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Year 4 maturity</t>
         </is>
       </c>
-      <c r="C11" s="87" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" s="87" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="47" t="inlineStr">
+      <c r="C11" s="52" t="n">
+        <v>11637</v>
+      </c>
+      <c r="D11" s="52" t="n">
+        <v>11637</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Year 5 maturity</t>
         </is>
       </c>
-      <c r="C12" s="87" t="n">
-        <v>125</v>
-      </c>
-      <c r="D12" s="87" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="47" t="inlineStr">
+      <c r="C12" s="52" t="n">
+        <v>19782.9</v>
+      </c>
+      <c r="D12" s="52" t="n">
+        <v>19782.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="C13" s="86" t="n">
+      <c r="C13" s="52" t="n">
         <v>75543</v>
       </c>
-      <c r="D13" s="87" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="47" t="inlineStr">
+      <c r="D13" s="52" t="n">
+        <v>75543</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Committed lines</t>
         </is>
       </c>
-      <c r="C14" s="87" t="n">
-        <v>50</v>
-      </c>
-      <c r="D14" s="87" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="47" t="inlineStr">
+      <c r="C14" s="52" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="52" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Tranche 1 amount</t>
         </is>
       </c>
-      <c r="C15" s="87" t="n">
-        <v>300</v>
-      </c>
-      <c r="D15" s="87" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="47" t="inlineStr">
+      <c r="C15" s="52" t="n">
+        <v>44937</v>
+      </c>
+      <c r="D15" s="52" t="n">
+        <v>44937</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tranche 1 rate</t>
         </is>
       </c>
-      <c r="C16" s="88" t="n">
+      <c r="C16" s="53" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="D16" s="53" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tranche 2 amount</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="n">
+        <v>22190</v>
+      </c>
+      <c r="D17" s="52" t="n">
+        <v>22190</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tranche 2 rate</t>
+        </is>
+      </c>
+      <c r="C18" s="53" t="n">
+        <v>0.05693742</v>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>0.05693742</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>109433</v>
+      </c>
+      <c r="D19" s="52" t="n">
+        <v>83383</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Maximum maturity concentration</t>
+        </is>
+      </c>
+      <c r="C20" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Minimum interest coverage</t>
+        </is>
+      </c>
+      <c r="C21" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="54" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Maximum weighted cost</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="n">
         <v>0.06</v>
       </c>
-      <c r="D16" s="88" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>Tranche 2 amount</t>
-        </is>
-      </c>
-      <c r="C17" s="87" t="n">
-        <v>150</v>
-      </c>
-      <c r="D17" s="87" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="B18" s="47" t="inlineStr">
-        <is>
-          <t>Tranche 2 rate</t>
-        </is>
-      </c>
-      <c r="C18" s="88" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D18" s="88" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="48">
-      <c r="B19" s="47" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C19" s="87" t="n">
-        <v>150</v>
-      </c>
-      <c r="D19" s="87" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="B20" s="47" t="inlineStr">
-        <is>
-          <t>Maximum maturity concentration</t>
-        </is>
-      </c>
-      <c r="C20" s="88" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D20" s="88" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="B21" s="47" t="inlineStr">
-        <is>
-          <t>Minimum interest coverage</t>
-        </is>
-      </c>
-      <c r="C21" s="89" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="89" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="48">
-      <c r="B22" s="47" t="inlineStr">
-        <is>
-          <t>Maximum weighted cost</t>
-        </is>
-      </c>
-      <c r="C22" s="88" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D22" s="88" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="48">
-      <c r="B26" s="47" t="inlineStr">
+      <c r="D22" s="53" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Ending debt</t>
         </is>
       </c>
-      <c r="C26" s="90">
+      <c r="C26" s="34">
         <f>MAX(0,C5+C6-C7)</f>
         <v/>
       </c>
-      <c r="D26" s="90">
+      <c r="D26" s="34">
         <f>MAX(0,D5+D6-D7)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="48">
-      <c r="B27" s="47" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Near-term maturities</t>
         </is>
       </c>
-      <c r="C27" s="90">
+      <c r="C27" s="34">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D27" s="90">
+      <c r="D27" s="34">
         <f>D8+D9</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="48">
-      <c r="B28" s="47" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Refinancing gap</t>
         </is>
       </c>
-      <c r="C28" s="90">
+      <c r="C28" s="34">
         <f>MAX(0,C27-C13-C14)</f>
         <v/>
       </c>
-      <c r="D28" s="90">
+      <c r="D28" s="34">
         <f>MAX(0,D27-D13-D14)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="48">
-      <c r="B29" s="47" t="inlineStr">
+    <row r="29">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Maturity concentration</t>
         </is>
       </c>
-      <c r="C29" s="91">
+      <c r="C29" s="35">
         <f>IFERROR(MAX(C8:C12)/SUM(C8:C12),0)</f>
         <v/>
       </c>
-      <c r="D29" s="91">
+      <c r="D29" s="35">
         <f>IFERROR(MAX(D8:D12)/SUM(D8:D12),0)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="48">
-      <c r="B30" s="47" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Weighted cost</t>
         </is>
       </c>
-      <c r="C30" s="91">
+      <c r="C30" s="35">
         <f>IFERROR((C15*C16+C17*C18)/(C15+C17),0)</f>
         <v/>
       </c>
-      <c r="D30" s="91">
+      <c r="D30" s="35">
         <f>IFERROR((D15*D16+D17*D18)/(D15+D17),0)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="48">
-      <c r="B31" s="47" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="C31" s="90">
+      <c r="C31" s="34">
         <f>C26*C30</f>
         <v/>
       </c>
-      <c r="D31" s="90">
+      <c r="D31" s="34">
         <f>D26*D30</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="48">
-      <c r="B32" s="47" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C32" s="92">
+      <c r="C32" s="36">
         <f>IFERROR(C19/C31,0)</f>
         <v/>
       </c>
-      <c r="D32" s="92">
+      <c r="D32" s="36">
         <f>IFERROR(D19/D31,0)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="42" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="4"/>
-    <col width="54" customWidth="1" style="47" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="19.7" customHeight="1" s="48">
-      <c r="B2" s="84" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="29" t="inlineStr">
         <is>
           <t>Debt Finance Decision Dashboard and Independent Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="85" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Check / decision</t>
         </is>
       </c>
-      <c r="C4" s="85" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="D4" s="85" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E4" s="85" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Interpretation / action</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Debt rollforward residual</t>
         </is>
       </c>
-      <c r="C5" s="93">
+      <c r="C5" s="37">
         <f>'Refinancing &amp; Rates'!D26-MAX(0,'Refinancing &amp; Rates'!D5+'Refinancing &amp; Rates'!D6-'Refinancing &amp; Rates'!D7)</f>
         <v/>
       </c>
-      <c r="D5" s="94">
+      <c r="D5" s="38">
         <f>IF(ABS(C5)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E5" s="47" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Debt must reconcile to issuance and repayment.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Weighted-cost residual</t>
         </is>
       </c>
-      <c r="C6" s="93">
+      <c r="C6" s="37">
         <f>'Refinancing &amp; Rates'!D30*('Refinancing &amp; Rates'!D15+'Refinancing &amp; Rates'!D17)-('Refinancing &amp; Rates'!D15*'Refinancing &amp; Rates'!D16+'Refinancing &amp; Rates'!D17*'Refinancing &amp; Rates'!D18)</f>
         <v/>
       </c>
-      <c r="D6" s="94">
+      <c r="D6" s="38">
         <f>IF(ABS(C6)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
-      <c r="E6" s="47" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Weighted pricing must reconcile to tranche balances and rates.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Refinancing gap</t>
         </is>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="37">
         <f>'Refinancing &amp; Rates'!D28</f>
         <v/>
       </c>
-      <c r="D7" s="94">
+      <c r="D7" s="38">
         <f>IF(C7=0,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E7" s="47" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Near-term maturities must be covered by liquidity and committed facilities.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Maturity concentration</t>
         </is>
       </c>
-      <c r="C8" s="93">
+      <c r="C8" s="37">
         <f>'Refinancing &amp; Rates'!D29</f>
         <v/>
       </c>
-      <c r="D8" s="94">
+      <c r="D8" s="38">
         <f>IF(C8&lt;='Refinancing &amp; Rates'!D20,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E8" s="47" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Escalate concentrated maturity walls.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="47" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C9" s="93">
+      <c r="C9" s="37">
         <f>'Refinancing &amp; Rates'!D32</f>
         <v/>
       </c>
-      <c r="D9" s="94">
+      <c r="D9" s="38">
         <f>IF(C9&gt;='Refinancing &amp; Rates'!D21,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E9" s="47" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>EBITDA must cover pro forma cash interest.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="47" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Weighted refinancing cost</t>
         </is>
       </c>
-      <c r="C10" s="93">
+      <c r="C10" s="37">
         <f>'Refinancing &amp; Rates'!D30</f>
         <v/>
       </c>
-      <c r="D10" s="94">
+      <c r="D10" s="38">
         <f>IF(C10&lt;='Refinancing &amp; Rates'!D22,"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E10" s="47" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Escalate expensive issuance and rate-reset risk.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="95" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Overall model status</t>
         </is>
       </c>
-      <c r="C12" s="96">
+      <c r="C12" s="40">
         <f>IF(COUNTIF(D5:D10,"FAIL")+COUNTIF(D5:D10,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D10,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F63"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="47" min="2" max="2"/>
-    <col width="48" customWidth="1" style="47" min="3" max="3"/>
-    <col width="24" customWidth="1" style="47" min="4" max="4"/>
-    <col width="34" customWidth="1" style="47" min="5" max="5"/>
-    <col width="20" customWidth="1" style="47" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="48">
-      <c r="B2" s="57" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>Debt Finance — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="58" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="59" t="inlineStr">
+      <c r="C4" s="43" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="58" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="59" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Debt Finance</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="58" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="59" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="58" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="59" t="inlineStr">
+      <c r="C7" s="43" t="inlineStr">
         <is>
           <t>tools/builders/build_debt_finance_release.py</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="58" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="59" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>issuer treasury, syndicate desk, rating agencies and board finance committee</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="58" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="59" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>financing alternatives and execution memo</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="58" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="59" t="inlineStr">
+      <c r="C10" s="43" t="inlineStr">
         <is>
           <t>daily during execution; monthly treasury</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="60" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="61" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="61" t="inlineStr">
+      <c r="C13" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="61" t="inlineStr">
+      <c r="D13" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="61" t="inlineStr">
+      <c r="E13" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="61" t="inlineStr">
+      <c r="F13" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="47" t="n">
+    <row r="14">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>all-in cost and break-even</t>
         </is>
       </c>
-      <c r="F14" s="47" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="47" t="n">
+    <row r="15">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="47" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>maturity and refinancing profile</t>
         </is>
       </c>
-      <c r="F15" s="47" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="47" t="n">
+    <row r="16">
+      <c r="B16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="47" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>ratings and covenant capacity</t>
         </is>
       </c>
-      <c r="F16" s="47" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="47" t="n">
+    <row r="17">
+      <c r="B17" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="47" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>base, downside and break-even outputs</t>
         </is>
       </c>
-      <c r="F17" s="47" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="B18" s="47" t="n">
+    <row r="18">
+      <c r="B18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="47" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>liquidity / funding requirement and binding constraint</t>
         </is>
       </c>
-      <c r="F18" s="47" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="B20" s="60" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="44" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="B21" s="61" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="61" t="inlineStr">
+      <c r="C21" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="61" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="61" t="inlineStr">
+      <c r="E21" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="61" t="inlineStr">
+      <c r="F21" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="48">
-      <c r="B22" s="47" t="n">
+    <row r="22">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="47" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Where is the break-even between fixed and floating?</t>
         </is>
       </c>
-      <c r="F22" s="47" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="48">
-      <c r="B23" s="47" t="n">
+    <row r="23">
+      <c r="B23" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="47" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>What flex can arrangers exercise?</t>
         </is>
       </c>
-      <c r="F23" s="47" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="48">
-      <c r="B24" s="47" t="n">
+    <row r="24">
+      <c r="B24" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="47" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Which maturities cluster under the downside?</t>
         </is>
       </c>
-      <c r="F24" s="47" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="48">
-      <c r="B25" s="47" t="n">
+    <row r="25">
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="47" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Which assumption is owner-approved versus modeler judgement?</t>
         </is>
       </c>
-      <c r="F25" s="47" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="48">
-      <c r="B26" s="47" t="n">
+    <row r="26">
+      <c r="B26" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="47" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>What fails first and who must act?</t>
         </is>
       </c>
-      <c r="F26" s="47" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="48">
-      <c r="B28" s="60" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="48">
-      <c r="B29" s="61" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="61" t="inlineStr">
+      <c r="C29" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="61" t="inlineStr">
+      <c r="D29" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="61" t="inlineStr">
+      <c r="E29" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="61" t="inlineStr">
+      <c r="F29" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="48">
-      <c r="B30" s="47" t="n">
+    <row r="30">
+      <c r="B30" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="47" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>base-rate and spread widening</t>
         </is>
       </c>
-      <c r="F30" s="47" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="48">
-      <c r="B31" s="47" t="n">
+    <row r="31">
+      <c r="B31" t="n">
         <v>2</v>
       </c>
-      <c r="C31" s="47" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>failed syndication / flex</t>
         </is>
       </c>
-      <c r="F31" s="47" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="48">
-      <c r="B32" s="47" t="n">
+    <row r="32">
+      <c r="B32" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>ratings downgrade</t>
         </is>
       </c>
-      <c r="F32" s="47" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="48">
-      <c r="B33" s="47" t="n">
+    <row r="33">
+      <c r="B33" t="n">
         <v>4</v>
       </c>
-      <c r="C33" s="47" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>data freshness / source failure</t>
         </is>
       </c>
-      <c r="F33" s="47" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="48">
-      <c r="B34" s="47" t="n">
+    <row r="34">
+      <c r="B34" t="n">
         <v>5</v>
       </c>
-      <c r="C34" s="47" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>combined severe-but-plausible downside</t>
         </is>
       </c>
-      <c r="F34" s="47" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="48">
-      <c r="B36" s="60" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="44" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="48">
-      <c r="B37" s="61" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="61" t="inlineStr">
+      <c r="C37" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="61" t="inlineStr">
+      <c r="D37" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="61" t="inlineStr">
+      <c r="E37" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="61" t="inlineStr">
+      <c r="F37" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="48">
-      <c r="B38" s="47" t="n">
+    <row r="38">
+      <c r="B38" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="47" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>bank proposals and commitment letters</t>
         </is>
       </c>
-      <c r="F38" s="47" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="48">
-      <c r="B39" s="47" t="n">
+    <row r="39">
+      <c r="B39" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="47" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>indentures / credit agreements</t>
         </is>
       </c>
-      <c r="F39" s="47" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="48">
-      <c r="B40" s="47" t="n">
+    <row r="40">
+      <c r="B40" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="47" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>rating-agency feedback</t>
         </is>
       </c>
-      <c r="F40" s="47" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="48">
-      <c r="B41" s="47" t="n">
+    <row r="41">
+      <c r="B41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>approved model card and assumption register</t>
         </is>
       </c>
-      <c r="F41" s="47" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15" customHeight="1" s="48">
-      <c r="B42" s="47" t="n">
+    <row r="42">
+      <c r="B42" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="47" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>independent validation and challenge record</t>
         </is>
       </c>
-      <c r="F42" s="47" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1" s="48">
-      <c r="B44" s="60" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="44" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1" s="48">
-      <c r="B45" s="61" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="61" t="inlineStr">
+      <c r="C45" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="61" t="inlineStr">
+      <c r="D45" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="61" t="inlineStr">
+      <c r="E45" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="61" t="inlineStr">
+      <c r="F45" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15" customHeight="1" s="48">
-      <c r="B46" s="47" t="n">
+    <row r="46">
+      <c r="B46" t="n">
         <v>1</v>
       </c>
-      <c r="C46" s="47" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>sources and uses balance</t>
         </is>
       </c>
-      <c r="F46" s="47" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1" s="48">
-      <c r="B47" s="47" t="n">
+    <row r="47">
+      <c r="B47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" s="47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>all-in yield includes fees and OID</t>
         </is>
       </c>
-      <c r="F47" s="47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1" s="48">
-      <c r="B48" s="47" t="n">
+    <row r="48">
+      <c r="B48" t="n">
         <v>3</v>
       </c>
-      <c r="C48" s="47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>maturity ladder equals debt ledger</t>
         </is>
       </c>
-      <c r="F48" s="47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" s="48">
-      <c r="B49" s="47" t="n">
+    <row r="49">
+      <c r="B49" t="n">
         <v>4</v>
       </c>
-      <c r="C49" s="47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>source-to-model lineage is reproducible</t>
         </is>
       </c>
-      <c r="F49" s="47" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="15" customHeight="1" s="48">
-      <c r="B50" s="47" t="n">
+    <row r="50">
+      <c r="B50" t="n">
         <v>5</v>
       </c>
-      <c r="C50" s="47" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>units, signs, dates and legal definitions reconcile</t>
         </is>
       </c>
-      <c r="F50" s="47" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="48">
-      <c r="B52" s="60" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15" customHeight="1" s="48">
-      <c r="B53" s="61" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="45" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="61" t="inlineStr">
+      <c r="C53" s="45" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="61" t="inlineStr">
+      <c r="D53" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="61" t="inlineStr">
+      <c r="E53" s="45" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="61" t="inlineStr">
+      <c r="F53" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1" s="48">
-      <c r="B54" s="47" t="n">
+    <row r="54">
+      <c r="B54" t="n">
         <v>1</v>
       </c>
-      <c r="C54" s="47" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>quoting coupon instead of all-in cost</t>
         </is>
       </c>
-      <c r="F54" s="47" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="48">
-      <c r="B55" s="47" t="n">
+    <row r="55">
+      <c r="B55" t="n">
         <v>2</v>
       </c>
-      <c r="C55" s="47" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>missing ticking fees and flex</t>
         </is>
       </c>
-      <c r="F55" s="47" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="48">
-      <c r="B56" s="47" t="n">
+    <row r="56">
+      <c r="B56" t="n">
         <v>3</v>
       </c>
-      <c r="C56" s="47" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>assuming refinancing proceeds before conditions</t>
         </is>
       </c>
-      <c r="F56" s="47" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="48">
-      <c r="B57" s="47" t="n">
+    <row r="57">
+      <c r="B57" t="n">
         <v>4</v>
       </c>
-      <c r="C57" s="47" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>stale vintage presented as current</t>
         </is>
       </c>
-      <c r="F57" s="47" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="48">
-      <c r="B58" s="47" t="n">
+    <row r="58">
+      <c r="B58" t="n">
         <v>5</v>
       </c>
-      <c r="C58" s="47" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>decision output disconnected from a binding constraint</t>
         </is>
       </c>
-      <c r="F58" s="47" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="48">
-      <c r="B60" s="60" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="48">
-      <c r="B61" s="61" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="45" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="61" t="inlineStr">
+      <c r="C61" s="45" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="61" t="inlineStr">
+      <c r="D61" s="45" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="61" t="inlineStr">
+      <c r="E61" s="45" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F61" s="45" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="48">
-      <c r="B62" s="47" t="inlineStr">
+    <row r="62">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Federal Reserve SR 26-2 Model Risk Management</t>
         </is>
       </c>
-      <c r="C62" s="47" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>governance, validation, change control, monitoring</t>
         </is>
       </c>
-      <c r="D62" s="47" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
         </is>
       </c>
-      <c r="E62" s="47" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Map explicitly</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="48">
-      <c r="B63" s="47" t="inlineStr">
+    <row r="63">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Basel SRP31 IRRBB</t>
         </is>
       </c>
-      <c r="C63" s="47" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>EVE/NII, basis and option risk</t>
         </is>
       </c>
-      <c r="D63" s="47" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://www.bis.org/basel_framework/chapter/SRP/31.htm</t>
         </is>
       </c>
-      <c r="E63" s="47" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Map explicitly</t>
         </is>
@@ -3374,928 +3239,684 @@
     <mergeCell ref="B52:F52"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F14:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F22:F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F30:F34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F38:F42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F46:F50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F54:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I54"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="47" min="2" max="2"/>
-    <col width="22" customWidth="1" style="47" min="3" max="3"/>
-    <col width="52" customWidth="1" style="47" min="4" max="4"/>
-    <col width="46" customWidth="1" style="47" min="5" max="5"/>
-    <col width="36" customWidth="1" style="47" min="6" max="6"/>
-    <col width="14" customWidth="1" style="47" min="7" max="7"/>
-    <col width="18" customWidth="1" style="47" min="8" max="8"/>
-    <col width="14" customWidth="1" style="47" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="48">
-      <c r="B2" s="57" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="61" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="61" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="61" t="inlineStr">
+      <c r="G4" s="45" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="61" t="inlineStr">
+      <c r="H4" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="61" t="inlineStr">
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="D5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="D5" t="inlineStr">
         <is>
           <t>sources and uses balance</t>
         </is>
       </c>
-      <c r="H5" s="47" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="D6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="D6" t="inlineStr">
         <is>
           <t>all-in yield includes fees and OID</t>
         </is>
       </c>
-      <c r="H6" s="47" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="D7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="D7" t="inlineStr">
         <is>
           <t>maturity ladder equals debt ledger</t>
         </is>
       </c>
-      <c r="H7" s="47" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="D8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="D8" t="inlineStr">
         <is>
           <t>source-to-model lineage is reproducible</t>
         </is>
       </c>
-      <c r="H8" s="47" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="D9" s="47" t="inlineStr">
+    <row r="9">
+      <c r="D9" t="inlineStr">
         <is>
           <t>units, signs, dates and legal definitions reconcile</t>
         </is>
       </c>
-      <c r="H9" s="47" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="H10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="H11" s="47" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="H12" s="47" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="H13" s="47" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="H14" s="47" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="H15" s="47" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="H16" s="47" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="H17" s="47" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="H18" s="47" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="48">
-      <c r="H19" s="47" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="H20" s="47" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="H21" s="47" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="48">
-      <c r="H22" s="47" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="48">
-      <c r="H23" s="47" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="48">
-      <c r="H24" s="47" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="48">
-      <c r="H25" s="47" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="48">
-      <c r="H26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="48">
-      <c r="H27" s="47" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="48">
-      <c r="H28" s="47" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="48">
-      <c r="H29" s="47" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="48">
-      <c r="H30" s="47" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="48">
-      <c r="H31" s="47" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="48">
-      <c r="H32" s="47" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="48">
-      <c r="H33" s="47" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="48">
-      <c r="H34" s="47" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="48">
-      <c r="H35" s="47" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="48">
-      <c r="H36" s="47" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="48">
-      <c r="H37" s="47" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="48">
-      <c r="H38" s="47" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="48">
-      <c r="H39" s="47" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="48">
-      <c r="H40" s="47" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="48">
-      <c r="H41" s="47" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="48">
-      <c r="H42" s="47" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="48">
-      <c r="H43" s="47" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="48">
-      <c r="H44" s="47" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="48">
-      <c r="H45" s="47" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="48">
-      <c r="H46" s="47" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="48">
-      <c r="H47" s="47" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="48">
-      <c r="H48" s="47" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="48">
-      <c r="H49" s="47" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="48">
-      <c r="H50" s="47" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="48">
-      <c r="H51" s="47" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="48">
-      <c r="H52" s="47" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="48">
-      <c r="H53" s="47" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="48">
-      <c r="H54" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H5:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G5:G54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="47" min="2" max="2"/>
-    <col width="18" customWidth="1" style="47" min="3" max="3"/>
-    <col width="42" customWidth="1" style="47" min="4" max="4"/>
-    <col width="24" customWidth="1" style="47" min="5" max="5"/>
-    <col width="18" customWidth="1" style="47" min="6" max="6"/>
-    <col width="22" customWidth="1" style="47" min="7" max="7"/>
-    <col width="42" customWidth="1" style="47" min="8" max="8"/>
-    <col width="30" customWidth="1" style="47" min="9" max="9"/>
-    <col width="15" customWidth="1" style="47" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18.55" customHeight="1" s="48">
-      <c r="B2" s="57" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="61" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="45" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="45" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="61" t="inlineStr">
+      <c r="E4" s="45" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="61" t="inlineStr">
+      <c r="F4" s="45" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="61" t="inlineStr">
+      <c r="G4" s="45" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="61" t="inlineStr">
+      <c r="H4" s="45" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="61" t="inlineStr">
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="61" t="inlineStr">
+      <c r="J4" s="45" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>debt ledger</t>
         </is>
       </c>
-      <c r="C5" s="47" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>daily/weekly</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>principal and legal-entity reconciliation</t>
         </is>
       </c>
-      <c r="J5" s="47" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>curves and spreads</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>timestamped executable levels</t>
         </is>
       </c>
-      <c r="J6" s="47" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>model governance evidence</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>per release</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>version, reviewer, sign-off and change log</t>
         </is>
       </c>
-      <c r="J7" s="47" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>decision-use snapshot</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>per decision</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>immutable as-of date and source receipt</t>
         </is>
       </c>
-      <c r="J8" s="47" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>TO MAP</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="J9" s="47" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="J10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="J11" s="47" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="J12" s="47" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="J13" s="47" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="J14" s="47" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="J15" s="47" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="J16" s="47" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="J17" s="47" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="J18" s="47" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="48">
-      <c r="J19" s="47" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="J20" s="47" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="J21" s="47" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="48">
-      <c r="J22" s="47" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="48">
-      <c r="J23" s="47" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="48">
-      <c r="J24" s="47" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="48">
-      <c r="J25" s="47" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="48">
-      <c r="J26" s="47" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="48">
-      <c r="J27" s="47" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="48">
-      <c r="J28" s="47" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="48">
-      <c r="J29" s="47" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="48">
-      <c r="J30" s="47" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="48">
-      <c r="J31" s="47" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="48">
-      <c r="J32" s="47" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="48">
-      <c r="J33" s="47" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="48">
-      <c r="J34" s="47" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="48">
-      <c r="J35" s="47" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="48">
-      <c r="J36" s="47" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="48">
-      <c r="J37" s="47" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="48">
-      <c r="J38" s="47" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="48">
-      <c r="J39" s="47" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="48">
-      <c r="J40" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J5:J40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="36" customWidth="1" style="47" min="2" max="2"/>
-    <col width="15" customWidth="1" style="47" min="3" max="5"/>
-    <col width="30" customWidth="1" style="47" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Issuance &amp; Capital Structure Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
-        <v>120</v>
-      </c>
-      <c r="D5" s="63" t="n">
-        <v>95</v>
-      </c>
-      <c r="E5" s="64">
+      <c r="C5" s="47" t="n">
+        <v>109433</v>
+      </c>
+      <c r="D5" s="47" t="n">
+        <v>83383</v>
+      </c>
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
-        <v>40</v>
-      </c>
-      <c r="D6" s="63" t="n">
-        <v>25</v>
-      </c>
-      <c r="E6" s="64">
+      <c r="C6" s="47" t="n">
+        <v>18315</v>
+      </c>
+      <c r="D6" s="47" t="n">
+        <v>13931</v>
+      </c>
+      <c r="E6" s="10">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Revolver drawn</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" s="63" t="n">
-        <v>75</v>
-      </c>
-      <c r="E7" s="64">
+      <c r="C7" s="47" t="n">
+        <v>6693</v>
+      </c>
+      <c r="D7" s="47" t="n">
+        <v>6693</v>
+      </c>
+      <c r="E7" s="10">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Term loan</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
-        <v>300</v>
-      </c>
-      <c r="D8" s="63" t="n">
-        <v>300</v>
-      </c>
-      <c r="E8" s="64">
+      <c r="C8" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="47" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Senior notes</t>
         </is>
       </c>
-      <c r="C9" s="63" t="n">
-        <v>250</v>
-      </c>
-      <c r="D9" s="63" t="n">
-        <v>250</v>
-      </c>
-      <c r="E9" s="64">
+      <c r="C9" s="47" t="n">
+        <v>44937</v>
+      </c>
+      <c r="D9" s="47" t="n">
+        <v>49781</v>
+      </c>
+      <c r="E9" s="10">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="47" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Other debt</t>
         </is>
       </c>
-      <c r="C10" s="63" t="n">
-        <v>50</v>
-      </c>
-      <c r="D10" s="63" t="n">
-        <v>50</v>
-      </c>
-      <c r="E10" s="64">
+      <c r="C10" s="47" t="n">
+        <v>15497</v>
+      </c>
+      <c r="D10" s="47" t="n">
+        <v>15497</v>
+      </c>
+      <c r="E10" s="10">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="47" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Base rate</t>
         </is>
       </c>
-      <c r="C11" s="65" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D11" s="65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E11" s="66">
+      <c r="C11" s="48" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="D11" s="48" t="n">
+        <v>0.0533</v>
+      </c>
+      <c r="E11" s="12">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="47" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Revolver spread</t>
         </is>
       </c>
-      <c r="C12" s="65" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="D12" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E12" s="66">
+      <c r="C12" s="48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="48" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="12">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="47" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Term loan spread</t>
         </is>
       </c>
-      <c r="C13" s="65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D13" s="65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E13" s="66">
+      <c r="C13" s="48" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D13" s="48" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="E13" s="12">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="47" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Senior notes coupon</t>
         </is>
       </c>
-      <c r="C14" s="65" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="D14" s="65" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14" s="66">
+      <c r="C14" s="48" t="n">
+        <v>0.04302793</v>
+      </c>
+      <c r="D14" s="48" t="n">
+        <v>0.04302793</v>
+      </c>
+      <c r="E14" s="12">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="47" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>New issue spread</t>
         </is>
       </c>
-      <c r="C15" s="65" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="D15" s="65" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E15" s="66">
+      <c r="C15" s="48" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="D15" s="48" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="E15" s="12">
         <f>IF(Cover!$C$9="Downside",D15,C15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="47" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>OID / fees</t>
         </is>
       </c>
-      <c r="C16" s="65" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="D16" s="65" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E16" s="66">
+      <c r="C16" s="48" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="D16" s="48" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="E16" s="12">
         <f>IF(Cover!$C$9="Downside",D16,C16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="47" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Minimum cash</t>
         </is>
       </c>
-      <c r="C17" s="63" t="n">
-        <v>25</v>
-      </c>
-      <c r="D17" s="63" t="n">
-        <v>30</v>
-      </c>
-      <c r="E17" s="64">
+      <c r="C17" s="47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D17" s="47" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="10">
         <f>IF(Cover!$C$9="Downside",D17,C17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="B18" s="47" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Max leverage</t>
         </is>
       </c>
-      <c r="C18" s="67" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D18" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="68">
+      <c r="C18" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14">
         <f>IF(Cover!$C$9="Downside",D18,C18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="48">
-      <c r="B19" s="47" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Min interest coverage</t>
         </is>
       </c>
-      <c r="C19" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="67" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="E19" s="68">
+      <c r="C19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="14">
         <f>IF(Cover!$C$9="Downside",D19,C19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="48">
-      <c r="B20" s="47" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Recovery multiple</t>
         </is>
       </c>
-      <c r="C20" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="D20" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" s="68">
+      <c r="C20" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="14">
         <f>IF(Cover!$C$9="Downside",D20,C20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="48">
-      <c r="B21" s="47" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>EV haircut</t>
         </is>
       </c>
-      <c r="C21" s="65" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D21" s="65" t="n">
+      <c r="C21" s="48" t="n">
         <v>0.35</v>
       </c>
-      <c r="E21" s="66">
+      <c r="D21" s="48" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E21" s="12">
         <f>IF(Cover!$C$9="Downside",D21,C21)</f>
         <v/>
       </c>
@@ -4304,247 +3925,245 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="28" customWidth="1" style="47" min="2" max="2"/>
-    <col width="16" customWidth="1" style="47" min="3" max="3"/>
-    <col width="14" customWidth="1" style="47" min="4" max="4"/>
-    <col width="18" customWidth="1" style="47" min="5" max="5"/>
-    <col width="12" customWidth="1" style="47" min="6" max="6"/>
-    <col width="14" customWidth="1" style="47" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Current Capital Structure</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Balance</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Annual interest</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Seniority</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Secured?</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Revolver</t>
         </is>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="15">
         <f>Assumptions!E7</f>
         <v/>
       </c>
-      <c r="D5" s="70">
+      <c r="D5" s="16">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="15">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="47" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" s="47" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Term loan</t>
         </is>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="15">
         <f>Assumptions!E8</f>
         <v/>
       </c>
-      <c r="D6" s="70">
+      <c r="D6" s="16">
         <f>Assumptions!E11+Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="15">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="47" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G6" s="47" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Senior notes</t>
         </is>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="15">
         <f>Assumptions!E9</f>
         <v/>
       </c>
-      <c r="D7" s="70">
+      <c r="D7" s="16">
         <f>Assumptions!E14</f>
         <v/>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="15">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="47" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G7" s="47" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Other debt</t>
         </is>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="15">
         <f>Assumptions!E10</f>
         <v/>
       </c>
-      <c r="D8" s="70">
+      <c r="D8" s="16">
         <f>Assumptions!E14</f>
         <v/>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="15">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="47" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G8" s="47" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Varies</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="71" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Gross debt</t>
         </is>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="18">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="71" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Net debt</t>
         </is>
       </c>
-      <c r="C11" s="72">
+      <c r="C11" s="18">
         <f>C10-Assumptions!E6</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="71" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="C12" s="72">
+      <c r="C12" s="18">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="48">
-      <c r="B13" s="71" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Gross leverage</t>
         </is>
       </c>
-      <c r="C13" s="73">
+      <c r="C13" s="19">
         <f>IFERROR(C10/Assumptions!E5,0)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="48">
-      <c r="B14" s="71" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>Net leverage</t>
         </is>
       </c>
-      <c r="C14" s="73">
+      <c r="C14" s="19">
         <f>IFERROR(C11/Assumptions!E5,0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="71" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="19">
         <f>IFERROR(Assumptions!E5/C12,0)</f>
         <v/>
       </c>
@@ -4553,271 +4172,274 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:H18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="26" customWidth="1" style="47" min="2" max="2"/>
-    <col width="13" customWidth="1" style="47" min="3" max="8"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Contractual Maturity Ladder</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Instrument</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="62" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Beyond</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Revolver</t>
         </is>
       </c>
-      <c r="C5" s="63" t="n">
+      <c r="C5" s="47" t="n">
+        <v>6693</v>
+      </c>
+      <c r="D5" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="63" t="n">
+      <c r="E5" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="63" t="n">
-        <v>25</v>
-      </c>
-      <c r="F5" s="63" t="n">
+      <c r="F5" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="63" t="n">
+      <c r="G5" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="63" t="n">
+      <c r="H5" s="47" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Term loan</t>
         </is>
       </c>
-      <c r="C6" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="63" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" s="63" t="n">
-        <v>288</v>
-      </c>
-      <c r="H6" s="63" t="n">
+      <c r="C6" s="47" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
+      <c r="D6" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Senior notes</t>
         </is>
       </c>
-      <c r="C7" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="63" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
+      <c r="C7" s="47" t="n">
+        <v>2249</v>
+      </c>
+      <c r="D7" s="47" t="n">
+        <v>8537.6</v>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>6830.1</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <v>5976.3</v>
+      </c>
+      <c r="G7" s="47" t="n">
+        <v>5122.6</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>16221.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Other debt</t>
         </is>
       </c>
-      <c r="C8" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="63" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="71" t="inlineStr">
+      <c r="C8" s="47" t="n">
+        <v>4649.1</v>
+      </c>
+      <c r="D8" s="47" t="n">
+        <v>3409.3</v>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>2479.5</v>
+      </c>
+      <c r="F8" s="47" t="n">
+        <v>1859.6</v>
+      </c>
+      <c r="G8" s="47" t="n">
+        <v>1549.7</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <v>1549.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Total maturities</t>
         </is>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="18">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="18">
         <f>SUM(D5:D8)</f>
         <v/>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="18">
         <f>SUM(E5:E8)</f>
         <v/>
       </c>
-      <c r="F10" s="72">
+      <c r="F10" s="18">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
-      <c r="G10" s="72">
+      <c r="G10" s="18">
         <f>SUM(G5:G8)</f>
         <v/>
       </c>
-      <c r="H10" s="72">
+      <c r="H10" s="18">
         <f>SUM(H5:H8)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="47" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cumulative maturities / gross debt</t>
         </is>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="16">
         <f>IFERROR(SUM($C$10:C10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="D12" s="70">
+      <c r="D12" s="16">
         <f>IFERROR(SUM($C$10:D10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="E12" s="70">
+      <c r="E12" s="16">
         <f>IFERROR(SUM($C$10:E10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="F12" s="70">
+      <c r="F12" s="16">
         <f>IFERROR(SUM($C$10:F10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="G12" s="70">
+      <c r="G12" s="16">
         <f>IFERROR(SUM($C$10:G10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
-      <c r="H12" s="70">
+      <c r="H12" s="16">
         <f>IFERROR(SUM($C$10:H10)/'Capital Structure'!$C$10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="48">
-      <c r="B15" s="47" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Near-term maturities (Years 1-2)</t>
         </is>
       </c>
-      <c r="C15" s="74">
+      <c r="C15" s="26">
         <f>SUM(C10:D10)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="48">
-      <c r="B16" s="47" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Available cash and committed lines</t>
         </is>
       </c>
-      <c r="C16" s="75" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="48">
-      <c r="B17" s="47" t="inlineStr">
+      <c r="C16" s="50" t="n">
+        <v>75543</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Refinancing gap</t>
         </is>
       </c>
-      <c r="C17" s="74">
+      <c r="C17" s="26">
         <f>MAX(0,C15-C16)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="48">
-      <c r="B18" s="47" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Largest maturity / total</t>
         </is>
       </c>
-      <c r="C18" s="76">
+      <c r="C18" s="28">
         <f>IFERROR(MAX(C10:H10)/SUM(C10:H10),0)</f>
         <v/>
       </c>
@@ -4826,186 +4448,184 @@
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="28" customWidth="1" style="47" min="2" max="2"/>
-    <col width="16" customWidth="1" style="47" min="3" max="3"/>
-    <col width="26" customWidth="1" style="47" min="4" max="4"/>
-    <col width="16" customWidth="1" style="47" min="5" max="5"/>
-    <col width="20" customWidth="1" style="47" min="6" max="6"/>
-    <col width="14" customWidth="1" style="47" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refinancing Sources &amp; Uses</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Uses</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Pricing / note</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="47" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Refinance current debt</t>
         </is>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="15">
         <f>'Capital Structure'!C10</f>
         <v/>
       </c>
-      <c r="D5" s="47" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>New term debt</t>
         </is>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="15">
+        <f>MIN(MAX(0,C8-E6),Assumptions!E18*Assumptions!E5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>Assumptions!E15+Assumptions!E16/7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Minimum cash funding</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>MAX(0,Assumptions!E17-Assumptions!E6)</f>
+        <v/>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Existing cash</t>
+        </is>
+      </c>
+      <c r="E6" s="15">
+        <f>MIN(MAX(0,Assumptions!E6-Assumptions!E17),C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fees / OID</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>C5*Assumptions!E16</f>
+        <v/>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Equity / other</t>
+        </is>
+      </c>
+      <c r="E7" s="15">
+        <f>MAX(0,C8-E5-E6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Total uses</t>
+        </is>
+      </c>
+      <c r="C8" s="15">
         <f>SUM(C5:C7)</f>
         <v/>
       </c>
-      <c r="F5" s="77">
-        <f>Assumptions!E15+Assumptions!E16/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="47" t="inlineStr">
-        <is>
-          <t>Minimum cash funding</t>
-        </is>
-      </c>
-      <c r="C6" s="69">
-        <f>MAX(0,Assumptions!E17-Assumptions!E6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>Existing cash</t>
-        </is>
-      </c>
-      <c r="E6" s="69">
-        <f>MAX(0,Assumptions!E6-Assumptions!E17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>Fees / OID</t>
-        </is>
-      </c>
-      <c r="C7" s="69">
-        <f>C5*Assumptions!E16</f>
-        <v/>
-      </c>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>Equity / other</t>
-        </is>
-      </c>
-      <c r="E7" s="69">
-        <f>MAX(0,C8-E5-E6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="47" t="inlineStr">
-        <is>
-          <t>Total uses</t>
-        </is>
-      </c>
-      <c r="C8" s="69">
-        <f>SUM(C5:C7)</f>
-        <v/>
-      </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Total sources</t>
         </is>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="15">
         <f>SUM(E5:E7)</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8">
         <f>IF(ABS(C8-E8)&lt;0.01,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="48">
-      <c r="B10" s="47" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Pro forma gross leverage</t>
         </is>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="21">
         <f>IFERROR(E5/Assumptions!E5,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="48">
-      <c r="B11" s="47" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Pro forma annual cash interest</t>
         </is>
       </c>
-      <c r="C11" s="69">
+      <c r="C11" s="15">
         <f>E5*F5</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="48">
-      <c r="B12" s="47" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Pro forma interest coverage</t>
         </is>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="21">
         <f>IFERROR(Assumptions!E5/C11,0)</f>
         <v/>
       </c>
@@ -5015,189 +4635,191 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="G8">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>G8="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>G8="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>G8="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>G8="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="47" min="1" max="1"/>
-    <col width="32" customWidth="1" style="47" min="2" max="2"/>
-    <col width="14" customWidth="1" style="47" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="48">
-      <c r="B2" s="49" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Interest Rate &amp; Spread Sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="48">
-      <c r="B4" s="62" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Base-rate shock / spread shock</t>
         </is>
       </c>
-      <c r="C4" s="79" t="n">
+      <c r="C4" s="22" t="n">
         <v>-100</v>
       </c>
-      <c r="D4" s="79" t="n">
+      <c r="D4" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="79" t="n">
+      <c r="E4" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="79" t="n">
+      <c r="F4" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="G4" s="79" t="n">
+      <c r="G4" s="22" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="48">
-      <c r="B5" s="80" t="n">
+    <row r="5">
+      <c r="B5" s="23" t="n">
         <v>-100</v>
       </c>
-      <c r="C5" s="69">
+      <c r="C5" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B5+C$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B5+C$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="D5" s="69">
+      <c r="D5" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B5+D$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B5+D$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="E5" s="69">
+      <c r="E5" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B5+E$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B5+E$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="F5" s="69">
+      <c r="F5" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B5+F$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B5+F$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="G5" s="69">
+      <c r="G5" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B5+G$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B5+G$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="48">
-      <c r="B6" s="80" t="n">
+    <row r="6">
+      <c r="B6" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="69">
+      <c r="C6" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B6+C$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B6+C$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="D6" s="69">
+      <c r="D6" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B6+D$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B6+D$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="E6" s="69">
+      <c r="E6" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B6+E$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B6+E$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="F6" s="69">
+      <c r="F6" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B6+F$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B6+F$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B6+G$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B6+G$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="48">
-      <c r="B7" s="80" t="n">
+    <row r="7">
+      <c r="B7" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B7+C$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B7+C$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="D7" s="69">
+      <c r="D7" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B7+D$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B7+D$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="E7" s="69">
+      <c r="E7" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B7+E$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B7+E$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="F7" s="69">
+      <c r="F7" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B7+F$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B7+F$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B7+G$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B7+G$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="48">
-      <c r="B8" s="80" t="n">
+    <row r="8">
+      <c r="B8" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B8+C$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B8+C$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="D8" s="69">
+      <c r="D8" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B8+D$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B8+D$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="E8" s="69">
+      <c r="E8" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B8+E$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B8+E$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="F8" s="69">
+      <c r="F8" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B8+F$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B8+F$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B8+G$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B8+G$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="48">
-      <c r="B9" s="80" t="n">
+    <row r="9">
+      <c r="B9" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="C9" s="69">
+      <c r="C9" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B9+C$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B9+C$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="D9" s="69">
+      <c r="D9" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B9+D$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B9+D$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="E9" s="69">
+      <c r="E9" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B9+E$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B9+E$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="F9" s="69">
+      <c r="F9" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B9+F$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B9+F$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
-      <c r="G9" s="69">
+      <c r="G9" s="15">
         <f>'Capital Structure'!$C$5*MAX(0,Assumptions!$E$11+Assumptions!$E$12+($B9+G$4)/10000)+'Capital Structure'!$C$6*MAX(0,Assumptions!$E$11+Assumptions!$E$13+($B9+G$4)/10000)+'Capital Structure'!$E$7+'Capital Structure'!$E$8</f>
         <v/>
       </c>
@@ -5207,19 +4829,17 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFE2F0D9"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFFCE4D6"/>
+        <cfvo type="max"/>
+        <color rgb="00E2F0D9"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00FCE4D6"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>